--- a/DATA/model_program.xlsx
+++ b/DATA/model_program.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{30653D24-464B-4F69-A4EB-F0662C17B7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{728C3265-30E3-4866-A06B-FC0FE97FB07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20475" yWindow="0" windowWidth="17280" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{095C6490-9A8D-4235-A476-97B526380A02}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="3" xr2:uid="{095C6490-9A8D-4235-A476-97B526380A02}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="5" r:id="rId1"/>
@@ -1358,7 +1358,1235 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>PBI!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Producto bruto interno por tipo de gasto (millones S/ 2007) - PBI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>PBI!$A$3:$A$62</c:f>
+              <c:strCache>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>T110</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>T210</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>T310</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>T410</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>T111</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>T211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>T311</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>T411</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>T112</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>T212</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>T312</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>T412</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>T113</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>T213</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>T313</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>T413</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>T114</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>T214</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>T314</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>T414</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>T115</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>T215</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>T315</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>T415</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>T116</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>T216</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>T316</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>T416</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>T117</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>T217</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>T317</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>T417</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>T118</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>T218</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>T318</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>T418</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>T119</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>T219</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>T319</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>T419</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>T120</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>T220</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>T320</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>T420</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>T121</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>T221</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>T321</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>T421</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>T122</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>T222</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>T322</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>T422</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>T123</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>T223</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>T323</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>T423</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>T124</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>T224</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>T324</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>T424</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PBI!$B$3:$B$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>87578.688233024805</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96843.879274328094</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96741.944733926503</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100904.520300736</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>94947.563581722905</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>101962.283589158</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>102364.289862155</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>106972.6143023</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>100749.44414052401</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>107971.584497394</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>109550.82835097901</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>112917.58164687001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>105765.24098878101</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>114735.405040294</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>115276.72312001001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>120645.674099474</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>111006.15700438101</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>116983.334304624</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>117378.26423999001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>121935.18421714701</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>113149.4203712</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>120698.861748585</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>121082.48595032599</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>127564.615886732</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>118217.24559821399</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>125207.210340167</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>126666.49622835001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>131480.70798639799</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>120917.358472768</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>128522.91161441299</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>130231.55172207901</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>134533.27709485599</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>124747.10682904</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>135716.38025113</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>133407.82504362401</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>140744.50333539501</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>127738.76847079401</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>137275.801035293</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>137929.707859591</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>143649.17681700599</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>123183.486627733</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>96028.496828261894</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>125946.366206192</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>141650.803661524</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>128358.638336718</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>136392.89377273299</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>140657.11359792101</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>146471.50810771901</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>133345.788783514</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>141036.723254107</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>143542.80216168999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>149462.87166954999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>133199.101081865</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>140427.20612333901</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>142597.47099672799</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>148877.412001905</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>135026.24537566199</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>145497.92528920801</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>148092.023399903</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>155150.116522667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A4BA-4F0E-8EA6-490F11B6D346}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="787406128"/>
+        <c:axId val="787418128"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="787406128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="787418128"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="787418128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="787406128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>80009</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>144779</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>154304</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>5714</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11DE60C2-FE6E-17D1-CE09-AD097CD9CB82}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -10569,6 +11797,7 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/DATA/model_program.xlsx
+++ b/DATA/model_program.xlsx
@@ -1,37 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{728C3265-30E3-4866-A06B-FC0FE97FB07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8594394E-1FDF-4B6A-B599-4959DE153F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="3" xr2:uid="{095C6490-9A8D-4235-A476-97B526380A02}"/>
+    <workbookView xWindow="8595" yWindow="0" windowWidth="18495" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{095C6490-9A8D-4235-A476-97B526380A02}"/>
   </bookViews>
   <sheets>
-    <sheet name="BD" sheetId="5" r:id="rId1"/>
+    <sheet name="BD" sheetId="5" state="hidden" r:id="rId1"/>
     <sheet name="bd-tri" sheetId="10" r:id="rId2"/>
-    <sheet name="Mensuales (2)" sheetId="9" r:id="rId3"/>
-    <sheet name="PBI" sheetId="2" r:id="rId4"/>
-    <sheet name="TIR" sheetId="3" r:id="rId5"/>
-    <sheet name="Tasa de encaje" sheetId="4" r:id="rId6"/>
-    <sheet name="Hoja1" sheetId="1" r:id="rId7"/>
-    <sheet name="base mone" sheetId="7" r:id="rId8"/>
-    <sheet name="Mensuales" sheetId="8" r:id="rId9"/>
-    <sheet name="M1" sheetId="11" r:id="rId10"/>
-    <sheet name="M2" sheetId="12" r:id="rId11"/>
-    <sheet name="M3- Bonos" sheetId="13" r:id="rId12"/>
-    <sheet name="Extras" sheetId="14" r:id="rId13"/>
+    <sheet name="Mensuales (2)" sheetId="9" state="hidden" r:id="rId3"/>
+    <sheet name="PBI" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="TIR" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="Tasa de encaje" sheetId="4" state="hidden" r:id="rId6"/>
+    <sheet name="Hoja1" sheetId="1" state="hidden" r:id="rId7"/>
+    <sheet name="base mone" sheetId="7" state="hidden" r:id="rId8"/>
+    <sheet name="Mensuales" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="M1" sheetId="11" state="hidden" r:id="rId10"/>
+    <sheet name="M2" sheetId="12" state="hidden" r:id="rId11"/>
+    <sheet name="M3- Bonos" sheetId="13" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TIR!$A$1:$B$182</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -277,7 +275,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="306">
   <si>
     <t>TIR</t>
   </si>
@@ -1087,9 +1085,6 @@
   </si>
   <si>
     <t>PN01063MM</t>
-  </si>
-  <si>
-    <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/mensuales/emision-primaria-y-multiplicador-millones-de-soles</t>
   </si>
   <si>
     <t>2016Q1</t>
@@ -1359,6 +1354,493 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-PE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'bd-tri'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> PBI </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'bd-tri'!$A$2:$A$37</c:f>
+              <c:strCache>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>2016Q1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2016Q2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2016Q3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2016Q4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2017Q1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2017Q2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2017Q3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2017Q4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2018Q1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2018Q2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2018Q3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2018Q4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2019Q1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2019Q2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2019Q3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2019Q4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2020Q1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2020Q2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2020Q3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2020Q4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2021Q1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2021Q2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2021Q3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2021Q4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2022Q1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2022Q2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2022Q3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2022Q4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2023Q1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2023Q2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2023Q3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2023Q4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024Q1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024Q2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024Q3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024Q4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'bd-tri'!$B$2:$B$37</c:f>
+              <c:numCache>
+                <c:formatCode>_ * #,##0_ ;_ * \-#,##0_ ;_ * "-"??_ ;_ @_ </c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>118217.24559821399</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>125207.210340167</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>126666.49622835001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>131480.70798639799</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>120917.358472768</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>128522.91161441299</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>130231.55172207901</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>134533.27709485599</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>124747.10682904</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>135716.38025113</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>133407.82504362401</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>140744.50333539501</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>127738.76847079401</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>137275.801035293</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>137929.707859591</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>143649.17681700599</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>123183.486627733</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>96028.496828261894</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>125946.366206192</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>141650.803661524</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>128358.638336718</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>136392.89377273299</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>140657.11359792101</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>146471.50810771901</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>133345.788783514</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>141036.723254107</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>143542.80216168999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>149462.87166954999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>133199.101081865</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>140427.20612333901</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>142597.47099672799</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>148877.412001905</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>135026.24537566199</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>145497.92528920801</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>148092.023399903</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>155150.116522667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-472B-456A-BC1A-E3434E7351D2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1993330719"/>
+        <c:axId val="1993331199"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1993330719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1993331199"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1993331199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-PE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1993330719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-PE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -2029,7 +2511,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2549,6 +3587,47 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182525A9-B7DB-252C-2A51-99E2627BA847}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>80009</xdr:colOff>
       <xdr:row>66</xdr:row>
@@ -2583,50 +3662,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>752475</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="9326277" cy="3896269"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CC1A737-CCDC-4A9F-B8DB-A7CBF573255F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="752475" y="733425"/>
-          <a:ext cx="9326277" cy="3896269"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8755,28 +9790,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3596D17-88FA-4C74-B42C-D9E80F7AD0BE}">
-  <dimension ref="B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="11.42578125" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{953ED9E0-C3A3-4BF3-A159-B1DDE0C5A9FC}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB2052DD-3D0B-48AD-9FE5-4D8EF10EC3E6}">
   <dimension ref="A1:M37"/>
@@ -8814,7 +9827,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B2" s="6">
         <v>118217.24559821399</v>
@@ -8835,7 +9848,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B3" s="6">
         <v>125207.210340167</v>
@@ -8856,7 +9869,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B4" s="6">
         <v>126666.49622835001</v>
@@ -8877,7 +9890,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B5" s="6">
         <v>131480.70798639799</v>
@@ -8898,7 +9911,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B6" s="6">
         <v>120917.358472768</v>
@@ -8919,7 +9932,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B7" s="6">
         <v>128522.91161441299</v>
@@ -8940,7 +9953,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B8" s="6">
         <v>130231.55172207901</v>
@@ -8961,7 +9974,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B9" s="6">
         <v>134533.27709485599</v>
@@ -8982,7 +9995,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B10" s="6">
         <v>124747.10682904</v>
@@ -9003,7 +10016,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B11" s="6">
         <v>135716.38025113</v>
@@ -9024,7 +10037,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B12" s="6">
         <v>133407.82504362401</v>
@@ -9045,7 +10058,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B13" s="6">
         <v>140744.50333539501</v>
@@ -9066,7 +10079,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" s="6">
         <v>127738.76847079401</v>
@@ -9087,7 +10100,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B15" s="6">
         <v>137275.801035293</v>
@@ -9108,7 +10121,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B16" s="6">
         <v>137929.707859591</v>
@@ -9129,7 +10142,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B17" s="6">
         <v>143649.17681700599</v>
@@ -9150,7 +10163,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B18" s="6">
         <v>123183.486627733</v>
@@ -9171,7 +10184,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B19" s="6">
         <v>96028.496828261894</v>
@@ -9192,7 +10205,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B20" s="6">
         <v>125946.366206192</v>
@@ -9213,7 +10226,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B21" s="6">
         <v>141650.803661524</v>
@@ -9234,7 +10247,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B22" s="6">
         <v>128358.638336718</v>
@@ -9255,7 +10268,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B23" s="6">
         <v>136392.89377273299</v>
@@ -9276,7 +10289,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B24" s="6">
         <v>140657.11359792101</v>
@@ -9297,7 +10310,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B25" s="6">
         <v>146471.50810771901</v>
@@ -9318,7 +10331,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B26" s="6">
         <v>133345.788783514</v>
@@ -9339,7 +10352,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B27" s="6">
         <v>141036.723254107</v>
@@ -9360,7 +10373,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B28" s="6">
         <v>143542.80216168999</v>
@@ -9381,7 +10394,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B29" s="6">
         <v>149462.87166954999</v>
@@ -9402,7 +10415,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B30" s="6">
         <v>133199.101081865</v>
@@ -9423,7 +10436,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B31" s="6">
         <v>140427.20612333901</v>
@@ -9444,7 +10457,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B32" s="6">
         <v>142597.47099672799</v>
@@ -9465,7 +10478,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B33" s="6">
         <v>148877.412001905</v>
@@ -9486,7 +10499,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B34" s="6">
         <v>135026.24537566199</v>
@@ -9507,7 +10520,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B35" s="6">
         <v>145497.92528920801</v>
@@ -9528,7 +10541,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B36" s="6">
         <v>148092.023399903</v>
@@ -9549,7 +10562,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B37" s="6">
         <v>155150.116522667</v>
@@ -9571,7 +10584,8 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/DATA/model_program.xlsx
+++ b/DATA/model_program.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29509"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebasteitor\Desktop\MODELOS ECONOMETRICOS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8594394E-1FDF-4B6A-B599-4959DE153F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F56D51C-B544-4A32-8E43-1256D55D0A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="0" windowWidth="18495" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{095C6490-9A8D-4235-A476-97B526380A02}"/>
+    <workbookView xWindow="6690" yWindow="0" windowWidth="18495" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{095C6490-9A8D-4235-A476-97B526380A02}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="5" state="hidden" r:id="rId1"/>
